--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260922.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.68%</t>
+          <t>11.83%</t>
         </is>
       </c>
     </row>
@@ -638,24 +638,24 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.50%</t>
+          <t>10.51%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>PWR US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>廣達服務公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>35,355</t>
+          <t>89,925</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>PWR US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>廣達服務公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>89,925</t>
+          <t>35,355</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>7.85%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.33%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>4.66%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>4.15%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.30%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
@@ -1144,24 +1144,24 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>27,369</t>
+          <t>50,910</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>50,910</t>
+          <t>27,369</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1254,90 +1254,90 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>30,114</t>
+          <t>8,904</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>202612ESZ6</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30,114</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>8,904</t>
+          <t>13,152</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>202612ESZ6</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,152</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>145,345</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,22 +1415,22 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>145,345</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1481,61 +1481,61 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>16,027</t>
+          <t>5,778</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>94,102</t>
+          <t>16,027</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>13,324</t>
+          <t>94,102</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,22 +1547,22 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>5,778</t>
+          <t>13,324</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>131,954,370</t>
+          <t>124,089,086</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
